--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.4108809953004</v>
+        <v>6.566768161736315</v>
       </c>
       <c r="D2" t="n">
-        <v>40.66017707782395</v>
+        <v>6.607278775146392</v>
       </c>
       <c r="E2" t="n">
-        <v>21.14996117008622</v>
+        <v>3.436868690139011</v>
       </c>
       <c r="F2" t="n">
-        <v>21.24317549165948</v>
+        <v>3.452016017394665</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.12002294940516</v>
+        <v>6.194503729278339</v>
       </c>
       <c r="D3" t="n">
-        <v>37.53664875824692</v>
+        <v>6.099705423215124</v>
       </c>
       <c r="E3" t="n">
-        <v>21.14996117008622</v>
+        <v>3.436868690139011</v>
       </c>
       <c r="F3" t="n">
-        <v>21.24317549165948</v>
+        <v>3.452016017394665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>84.08740904467243</v>
+        <v>13.66420396975927</v>
       </c>
       <c r="D4" t="n">
-        <v>84.08073111630183</v>
+        <v>13.66311880639905</v>
       </c>
       <c r="E4" t="n">
-        <v>21.14996117008622</v>
+        <v>3.436868690139011</v>
       </c>
       <c r="F4" t="n">
-        <v>21.24317549165948</v>
+        <v>3.452016017394665</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
